--- a/TextConverter/src/main/resources/step.xlsx
+++ b/TextConverter/src/main/resources/step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jamie\RemotelyBackedUp\Git\StepTextConversion\TextConverter\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBE1D69-DE5A-4015-BEF4-17E05A4D1216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C403DA-50BC-4448-81EE-F7A68E34C4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6810EFB2-CF9F-4B19-9246-F88FA22FDC5D}"/>
   </bookViews>
@@ -629,9 +629,6 @@
     <t xml:space="preserve">             Mainly for use in the Sword config file, but may also appear on the STEPBible copyright page.</t>
   </si>
   <si>
-    <t xml:space="preserve">                                           Details of the organisation which holds the text.  Often this will be the same as the opwning organisation, in which case you can leave these entries blank.  But eg for DBL texts you will need details for DBL.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">What it says on the tin.  You </t>
     </r>
@@ -740,6 +737,118 @@
     <t>This appears as the About parameter in Sword configuration files, and on the copyright page as the detailed copyright information.  Typically it gives copyright and permitted usage details (drawn from the fields above), but on some texts we go beyond this, for instance with background information about the translation.  It also includes acknowledgements and, on public modules, outline information about any changes we may have applied during processing.</t>
   </si>
   <si>
+    <t>#! Information to appear on the STEPBible Bible chooser.</t>
+  </si>
+  <si>
+    <t>Any copyright information or usage limitations from the text supplier.  On DBL texts it may be possible to pick this up from the metadata file, but you should check.  It is also worth looking on the websites of text suppliers to see if they supply more detailed information.
+You can either put all of the details into this one field, or you can split out various special parts of it into the fields above, in which case the system can apply standard formatting to it, to make it easier to read.
+If using multiple lines, don't forget to put backslash at the end of all but the last.</t>
+  </si>
+  <si>
+    <t>As stipulated by supplier.  Eg Can’t use more than 500 verses from one book.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+  </si>
+  <si>
+    <t>As stipulated by supplier.  Eg Have to acknowledge.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+  </si>
+  <si>
+    <t>Occasionally extended descriptive information is supplied by the text supplier, or we may want to add comments of our own.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+  </si>
+  <si>
+    <t>#! Textual copyright information.</t>
+  </si>
+  <si>
+    <t>Describing the text</t>
+  </si>
+  <si>
+    <t>Normally processing starts from eg USX if available.  This says to start from existing OSIS.  Required only other inputs are available in addition to OSIS.</t>
+  </si>
+  <si>
+    <t>#! Other settings you may require.  They are used as-is, and therefore need to be complete configuration statements eg myParm#=123.</t>
+  </si>
+  <si>
+    <t>#! There must be only one statement per box.  You can add more rows if you need them, but make sure you copy %AdditionalStatements#= or %AdditionalIncludes#= to each.</t>
+  </si>
+  <si>
+    <t>Any 'include' or 'includeIfExists' statements.</t>
+  </si>
+  <si>
+    <t>#! Processing mechanics.  Also affected by the section marked 'CONTROL' above.</t>
+  </si>
+  <si>
+    <t>swordTypeOfDocument#=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                           Details of the organisation which holds the text.  Often this will be the same as the owning organisation, in which case you can leave these entries blank.  But eg for DBL texts you will need details for DBL.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I don't police things here: I make the assumption that if you fail to supply a value which the spreadsheet describes as being required , it will be because you are going to include, from here, other textual config files which make good the deficit.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The converter automatically defaults as many parameters as possible, including many of these defined here.  However, if you supply a non-blank value here, it will override the default.
+A strong yellow arrow with a copy icon below indicates that the lower item will normally be a direct copy of the earlier one, and need therefore be filled in only if you want to override that value.
+A semi-transparent yellow arrow with a copy icon and a 'calculate' icon indicates that the converter normally works out a value for itself, but will take the value at the start of the arrow if the calculation fails.  Fill in the field at the end of the arrow if you want to override this and force a value.
+A white arrow with a 'calculate' icon indicates that the lower element is normally deduced from the earlier one, but is not a direct copy of it.  As before, you can fill in the lower box to force your own value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CAVEATS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Some of the 'Calculated' fields organise for other elements to be assembled into what we have adopted as a 'standard' order.  If you override these by supplying your own value, you will need to ensure that value contains the information we normally require in these fields, and that it is ordered appropriately.  Regrettably as things stand you can determine what the content and order should be only by reference to the various configuration files in the Resources section of the converter JAR, or by reference to the code, particularly that in ConfigData.kt.
+Similarly in a number of cases, fields are described as being potentially derived from DBL data where available.  Again, if you wish to find out how they are derived, you will need to have recourse to the built-in configutation files and the code.  You should be aware that deriving information from DBL is, in any case, somewhat of a black art, in that the DBL metadata doesn't seem to be documented anywhere, and people therefore apply their own interpretation in deciding which fields should be used for what purpose.  And then at the end of all this, increasingly we are deciding to override that data anyway.
+All of this means that you may well need to do one or two runs and examine the outputs until you achieve what you want.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -762,7 +871,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Fill in the cells below as appropriate.  They're colour-coded as follows:
+      <t xml:space="preserve">Fill in the cells below as appropriate.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Column E indicates acceptable types of data or specific options in some cases.  If not specified, fields can contain free-form text.)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Fields are colour-coded as follows:
 </t>
     </r>
     <r>
@@ -868,138 +999,6 @@
       <t>Optional.
    White:  These values are normally calculated but you can override them by providing your own values here if you wish (where there is no indication to the contrary).  In general, though, if it's white, you're unlikely to need to change it.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Note that I do not police things here: I make the assumption that if you fail to supply a required value here, it may be because you are going to include, from here, other textual config files which make good the deficit.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-The processing automatically includes commonRoot.conf (from the converter JAR resources section), which supplies reasonable defaults for all parameters.  It then applies any non-blank definitions below.  Such definitions will override </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>all</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> other settings, and therefore will definitely be used.
-A strong yellow arrow with a copy icon below indicates that the lower item will normally be a direct copy of the earlier one, and need therefore be filled in only if you want to override that value.
-A semi-transparent yellow arrow with a copy icon and a 'calculate' icon indicates that the lower item may be defaulted by the system in a variety of ways, depending upon the circumstances – with the value from the upper box being used as a last resort.  Once again, you can enter a value here to force things.
-A white arrow with a 'calculate' icon indicates that the lower element is normally deduced from the earlier one, but is not a direct copy of it.  As before, you can fill in the lower box to force your own value.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CAVEATS</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Some of the fields described as 'Calculated' rely upon quite complex calculations (calculations which, at present, I have decided are either too complicated to set out here, or are too liable to change).  You definitely can override these if you wish to, by giving values here, but bear in mind that the calculations may well be set up to organise things in a standard format which you may need to mimic.  Regrettably as things stand you can determine what that format is only by reference to the various configuration files in the Resources section of the converter JAR, or by reference to the code, particularly that in ConfigData.kt.
-Similarly in a number of cases, fields are described as being potentially derived from DBL data where available.  Again, if you wish to find out how they are derived, you will need to have recourse to the built-in configutation files and the code.  You should be aware that deriving information from DBL is, in any case, somewhat of a black art, in that the DBL metadata doesn't seem to be documented anywhere, and people therefore apply their own interpretation in deciding which fields should be used for what purpose.  And then at the end of all this, increasingly we are deciding to override that data anyway.
-All of this means that you may well need to do one or two runs and examine the outputs until you achieve what you want.</t>
-    </r>
-  </si>
-  <si>
-    <t>#! Information to appear on the STEPBible Bible chooser.</t>
-  </si>
-  <si>
-    <t>Any copyright information or usage limitations from the text supplier.  On DBL texts it may be possible to pick this up from the metadata file, but you should check.  It is also worth looking on the websites of text suppliers to see if they supply more detailed information.
-You can either put all of the details into this one field, or you can split out various special parts of it into the fields above, in which case the system can apply standard formatting to it, to make it easier to read.
-If using multiple lines, don't forget to put backslash at the end of all but the last.</t>
-  </si>
-  <si>
-    <t>As stipulated by supplier.  Eg Can’t use more than 500 verses from one book.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>As stipulated by supplier.  Eg Have to acknowledge.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>Occasionally extended descriptive information is supplied by the text supplier, or we may want to add comments of our own.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>#! Textual copyright information.</t>
-  </si>
-  <si>
-    <t>Describing the text</t>
-  </si>
-  <si>
-    <t>Normally processing starts from eg USX if available.  This says to start from existing OSIS.  Required only other inputs are available in addition to OSIS.</t>
-  </si>
-  <si>
-    <t>#! Other settings you may require.  They are used as-is, and therefore need to be complete configuration statements eg myParm#=123.</t>
-  </si>
-  <si>
-    <t>#! There must be only one statement per box.  You can add more rows if you need them, but make sure you copy %AdditionalStatements#= or %AdditionalIncludes#= to each.</t>
-  </si>
-  <si>
-    <t>Any 'include' or 'includeIfExists' statements.</t>
-  </si>
-  <si>
-    <t>#! Processing mechanics.  Also affected by the section marked 'CONTROL' above.</t>
-  </si>
-  <si>
-    <t>swordTypeOfDocument#=</t>
   </si>
 </sst>
 </file>
@@ -5445,7 +5444,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="57" customFormat="1" ht="192" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
@@ -5456,7 +5455,7 @@
     </row>
     <row r="2" spans="1:7" s="57" customFormat="1" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="67" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B2" s="68"/>
       <c r="C2" s="68"/>
@@ -5467,7 +5466,7 @@
     </row>
     <row r="3" spans="1:7" s="57" customFormat="1" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="70" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B3" s="68"/>
       <c r="C3" s="68"/>
@@ -6292,7 +6291,7 @@
         <v>118</v>
       </c>
       <c r="C78" s="61" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="D78" s="60"/>
       <c r="E78" s="43"/>
@@ -6403,7 +6402,7 @@
         <v>2</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G88" s="16"/>
     </row>
@@ -6427,7 +6426,7 @@
         <v>39</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G90" s="16"/>
     </row>
@@ -6543,7 +6542,7 @@
         <v>2</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G101" s="16"/>
     </row>
@@ -6614,7 +6613,7 @@
         <v>70</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G107" s="16"/>
     </row>
@@ -6631,14 +6630,14 @@
       <c r="A109" s="14"/>
       <c r="B109" s="18"/>
       <c r="C109" s="15" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="17" t="s">
         <v>71</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G109" s="16"/>
     </row>
@@ -6686,7 +6685,7 @@
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
       <c r="B114" s="33" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C114" s="34"/>
       <c r="D114" s="16"/>
@@ -6738,7 +6737,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G118" s="16"/>
     </row>
@@ -6786,7 +6785,7 @@
         <v>2</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G122" s="16"/>
     </row>
@@ -6810,7 +6809,7 @@
         <v>2</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G124" s="16"/>
     </row>
@@ -6834,7 +6833,7 @@
         <v>2</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G126" s="16"/>
     </row>
@@ -6850,10 +6849,10 @@
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="33" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C129" s="66" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="17"/>
@@ -6888,7 +6887,7 @@
         <v>2</v>
       </c>
       <c r="F132" s="48" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G132" s="54"/>
     </row>
@@ -6912,7 +6911,7 @@
         <v>2</v>
       </c>
       <c r="F134" s="48" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G134" s="16"/>
     </row>
@@ -6936,7 +6935,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="48" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G136" s="16"/>
     </row>
@@ -6960,7 +6959,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G138" s="16"/>
     </row>
@@ -7068,7 +7067,7 @@
         <v>2</v>
       </c>
       <c r="F148" s="48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G148" s="16"/>
     </row>
@@ -7101,7 +7100,7 @@
     <row r="152" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="14"/>
       <c r="B152" s="33" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C152" s="34"/>
       <c r="D152" s="16"/>
@@ -7153,7 +7152,7 @@
         <v>51</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G156" s="16"/>
     </row>
@@ -7177,7 +7176,7 @@
         <v>17</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G158" s="16"/>
     </row>
@@ -7198,10 +7197,10 @@
       </c>
       <c r="D160" s="19"/>
       <c r="E160" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G160" s="16"/>
     </row>
@@ -7288,7 +7287,7 @@
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="14"/>
       <c r="B169" s="33" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C169" s="34"/>
       <c r="D169" s="16"/>
@@ -7299,7 +7298,7 @@
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="14"/>
       <c r="B170" s="33" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C170" s="34"/>
       <c r="D170" s="16"/>
@@ -7377,7 +7376,7 @@
         <v>2</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G176" s="16"/>
     </row>

--- a/TextConverter/src/main/resources/step.xlsx
+++ b/TextConverter/src/main/resources/step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jamie\RemotelyBackedUp\Git\StepTextConversion\TextConverter\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C403DA-50BC-4448-81EE-F7A68E34C4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF18CD7B-936A-4392-A5F1-FD4EE8C84BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6810EFB2-CF9F-4B19-9246-F88FA22FDC5D}"/>
   </bookViews>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="152">
-  <si>
-    <t>#! Identification.</t>
-  </si>
-  <si>
-    <t>%Comment#=</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="155">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -51,39 +45,12 @@
     <t>DBL / Empty</t>
   </si>
   <si>
-    <t>The format of any external metadata which you wish to pick up.</t>
-  </si>
-  <si>
     <t>stepExternalMetadataFileName#=</t>
   </si>
   <si>
     <t>stepExternalLicenceFileName#=</t>
   </si>
   <si>
-    <t>stepStandardOwnerOrganisation#=</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Biblica / Absent</t>
-  </si>
-  <si>
-    <t>A selector for the owner organsation, if it is one of a standard list (which list currently comprises only Biblica).  Lets us pick up standard details of the organisation.</t>
-  </si>
-  <si>
-    <t>English Bible name as given by the translators.  User-supplied or taken from DBL.</t>
-  </si>
-  <si>
-    <t>English abbreviation as we want it on the Bible chooser.  User-supplied; if omitted, uses the AsSupplied version.</t>
-  </si>
-  <si>
-    <t>Vernacular Bible as we want it on the Bible chooser.  User-supplied; if omitted, uses the AsSupplied version.</t>
-  </si>
-  <si>
-    <t>Vernacular abbreviation as we want it on the Bible chooser.  User-supplied; if omitted, uses the AsSupplied version.</t>
-  </si>
-  <si>
-    <t>#! Copyright and ownership.</t>
-  </si>
-  <si>
     <t>stepIsCopyrightText#=</t>
   </si>
   <si>
@@ -96,15 +63,6 @@
     <t>swordShortCopyright#=</t>
   </si>
   <si>
-    <t>A brief copyright notice.  User supplied or taken from DBL.</t>
-  </si>
-  <si>
-    <t>stepEncryptionRequired#=</t>
-  </si>
-  <si>
-    <t>Yes if encryption required.  Defaults to Yes / No according to whether this is a copyright text, but ok to override.</t>
-  </si>
-  <si>
     <t>swordDistributionLicence#=</t>
   </si>
   <si>
@@ -114,36 +72,21 @@
     <t>swordTextOwnerOrganisationFullName#=</t>
   </si>
   <si>
-    <t>Full name of organisation which owns the text.</t>
-  </si>
-  <si>
     <t>swordTextOwnerOrganisationAbbreviatedName#=</t>
   </si>
   <si>
-    <t>Abbreviated name of organisation which owns the text.</t>
-  </si>
-  <si>
     <t>swordTextOwnerOrganisationWebsiteLinkOrDescription#=</t>
   </si>
   <si>
-    <t>Website of organisation which owns the text.</t>
-  </si>
-  <si>
     <t>swordTextRepositoryOrganisationFullName#=</t>
   </si>
   <si>
-    <t xml:space="preserve"> Arbitrary string</t>
-  </si>
-  <si>
     <t>Full name of organisation which holds the text.</t>
   </si>
   <si>
     <t>swordTextRepositoryOrganisationAbbreviatedName#=</t>
   </si>
   <si>
-    <t>Abbreviated name of organisation which holds the text.</t>
-  </si>
-  <si>
     <t>#! Language and script.</t>
   </si>
   <si>
@@ -180,12 +123,6 @@
     <t xml:space="preserve"> ScriptCode</t>
   </si>
   <si>
-    <t>stepOsis2modFilePath#=</t>
-  </si>
-  <si>
-    <t>Path to osis2mod executable.  Typically stored in the STEP environment variable.</t>
-  </si>
-  <si>
     <t>stepUseExistingOsis#=</t>
   </si>
   <si>
@@ -204,9 +141,6 @@
     <t xml:space="preserve"> None / Runtime</t>
   </si>
   <si>
-    <t>Says whether this run should apply reversification or not.  (Reversification is always applied on STEPBible runs.)</t>
-  </si>
-  <si>
     <t>stepReversificationFootnoteLevel#=</t>
   </si>
   <si>
@@ -222,9 +156,6 @@
     <t xml:space="preserve"> Yes / no</t>
   </si>
   <si>
-    <t>Says whether we have vernacular format information which can be used, eg, for validating references.</t>
-  </si>
-  <si>
     <t>#! Sword config file.  Parameters from other sections in this data also appear here, but these are the things which are specific to the Sword config file – either things which Sword requires as parameters, or things which appear in our admin comments.</t>
   </si>
   <si>
@@ -246,24 +177,12 @@
     <t>stepTextModifiedDate#=</t>
   </si>
   <si>
-    <t xml:space="preserve"> yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> As accepted by Sword</t>
-  </si>
-  <si>
     <t>swordTextIdSuppliedBySourceRepositoryOrOwnerOrganisation#=</t>
   </si>
   <si>
-    <t>Any identifier supplied by the repository or text owner.  Recorded in admin comments only, to let us tie things together.</t>
-  </si>
-  <si>
     <t>stepRightsHolderForBibleChooser#=</t>
   </si>
   <si>
-    <t>On a few texts we include rights holder information in the Bible chooser.  Enter something here if this is required.</t>
-  </si>
-  <si>
     <t>calcBibleNameForBibleChooser#=</t>
   </si>
   <si>
@@ -282,9 +201,6 @@
     <t>calcBibleChooserTextAssembly#=</t>
   </si>
   <si>
-    <t>swordCopyrightStatement#=</t>
-  </si>
-  <si>
     <t>swordUsageRights#=</t>
   </si>
   <si>
@@ -300,45 +216,18 @@
     <t>stepAddedValueMorphology#=</t>
   </si>
   <si>
-    <t>Says whether STEPBible has added morphology to the text.  Used on copyright page.</t>
-  </si>
-  <si>
     <t>stepAddedValueStrongs#=</t>
   </si>
   <si>
-    <t>Says whether STEPBible has added Strongs to the text.  Used on copyright page.</t>
-  </si>
-  <si>
     <t>%AdditionalStatements#=</t>
   </si>
   <si>
-    <t>%AdditionalIncludes#=</t>
-  </si>
-  <si>
-    <t>Template version 2.0</t>
-  </si>
-  <si>
-    <t>The path to the metadata file.  Defaults to @find/metadata.xml, but if you have a compelling reason to rename the file, give the name – @find/myFile.conf – here.</t>
-  </si>
-  <si>
-    <t>The path to the licence file.  Defaults to @find/license.xml, but if you have a compelling reason to rename the file, give the name – @find/myFile.conf – here.</t>
-  </si>
-  <si>
-    <t>#! External metadata details.  Relevant only if you intend to pick up data automatically from metadata files supplied to you (presently possible only for DBL texts).  This tells the system which files to use, and what format they are in.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> File-finder / Absent</t>
   </si>
   <si>
     <t>English Bible as we want it on the Bible chooser.  By default uses stepBibleNameEnglishAsSupplied, but you can override it here – eg for brevity.</t>
   </si>
   <si>
-    <t>English abbreviation as given by the translators.  Mandatory unless taken from DBL.</t>
-  </si>
-  <si>
-    <t>Vernacular abbreviation as given by the translators.  User-supplied or taken from DBL.  If not supplied defaults to the English equivalent stepAbbreviationEnglishAsSupplied.</t>
-  </si>
-  <si>
     <t>Outline details of licence – eg things like 'Used by permission'.</t>
   </si>
   <si>
@@ -346,18 +235,6 @@
   </si>
   <si>
     <t>Any general statements you may want.</t>
-  </si>
-  <si>
-    <t>Vernacular Bible name as given by the translators.  User-supplied or taken from DBL.  If not filled in, takes the value from DBL if possible, otherwise uses the English version stepBibleNameEnglishAsSupplied.</t>
-  </si>
-  <si>
-    <t>Should text be available online only?  Default is No; fill in Yes if that's what you require.</t>
-  </si>
-  <si>
-    <t>Yes / No.  Defaults to Yes, for safety's sake, so you need only fill in No where necessary.</t>
-  </si>
-  <si>
-    <t>We have some special processing built into the converter to cope with systematic idosyncrasies in the way a particular organisation represents its text.  At present we have this processing only for Biblica, so the only value you can usefully give here is Biblica.  Note that this setting is independent of the 'Biblica' against stepStandardOwnerOrganisation above.  That one determines whether we pick up standard metadata for Biblica, while this one determines if we do the Biblica-specific modifications to the texts.  If you want to do both, you need Biblica in both places.</t>
   </si>
   <si>
     <r>
@@ -566,6 +443,130 @@
       </rPr>
       <t>VernacularCanonicalForBibleChooser#=</t>
     </r>
+  </si>
+  <si>
+    <t>#! Text naming.  This information is used both in the STEPBible Bible chooser and (perhaps) on the copyright page.  If the English and vernacular details differ, both are used in some places.</t>
+  </si>
+  <si>
+    <t>#!</t>
+  </si>
+  <si>
+    <t>Controls certain aspects of the way the text can be handled.</t>
+  </si>
+  <si>
+    <t>2-character language code.  Ususally deduced from the 3-char code which appears in the name of the folder containing the text you are working on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> From predefined list</t>
+  </si>
+  <si>
+    <t>What is says on the tin.  You probably want to accept the calculated value, and can therefore leave this blank.</t>
+  </si>
+  <si>
+    <t>For non-English texts, the name of language if available.  You can override if necessary.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used where a text covers less than the full Protestant canon, to indicate coverage.  You can change this if you want to, but you probably </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>don't</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> want to, because the system will calculate it.</t>
+    </r>
+  </si>
+  <si>
+    <t>This appears as the About parameter in Sword configuration files, and on the copyright page as the detailed copyright information.  Typically it gives copyright and permitted usage details (drawn from the fields above), but on some texts we go beyond this, for instance with background information about the translation.  It also includes acknowledgements and, on public modules, outline information about any changes we may have applied during processing.</t>
+  </si>
+  <si>
+    <t>Any copyright information or usage limitations from the text supplier.  On DBL texts it may be possible to pick this up from the metadata file, but you should check.  It is also worth looking on the websites of text suppliers to see if they supply more detailed information.
+You can either put all of the details into this one field, or you can split out various special parts of it into the fields above, in which case the system can apply standard formatting to it, to make it easier to read.
+If using multiple lines, don't forget to put backslash at the end of all but the last.</t>
+  </si>
+  <si>
+    <t>Occasionally extended descriptive information is supplied by the text supplier, or we may want to add comments of our own.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+  </si>
+  <si>
+    <t>Normally processing starts from eg USX if available.  This says to start from existing OSIS.  Required only other inputs are available in addition to OSIS.</t>
+  </si>
+  <si>
+    <t>#! Other settings you may require.  They are used as-is, and therefore need to be complete configuration statements eg myParm#=123.</t>
+  </si>
+  <si>
+    <t>#! There must be only one statement per box.  You can add more rows if you need them, but make sure you copy %AdditionalStatements#= or %AdditionalIncludes#= to each.</t>
+  </si>
+  <si>
+    <t>#! Processing mechanics.  Also affected by the section marked 'CONTROL' above.</t>
+  </si>
+  <si>
+    <t>swordTypeOfDocument#=</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CAVEATS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Some of the 'Calculated' fields organise for other elements to be assembled into what we have adopted as a 'standard' order.  If you override these by supplying your own value, you will need to ensure that value contains the information we normally require in these fields, and that it is ordered appropriately.  Regrettably as things stand you can determine what the content and order should be only by reference to the various configuration files in the Resources section of the converter JAR, or by reference to the code, particularly that in ConfigData.kt.
+Similarly in a number of cases, fields are described as being potentially derived from DBL data where available.  Again, if you wish to find out how they are derived, you will need to have recourse to the built-in configutation files and the code.  You should be aware that deriving information from DBL is, in any case, somewhat of a black art, in that the DBL metadata doesn't seem to be documented anywhere, and people therefore apply their own interpretation in deciding which fields should be used for what purpose.  And then at the end of all this, increasingly we are deciding to override that data anyway.
+All of this means that you may well need to do one or two runs and examine the outputs until you achieve what you want.</t>
+    </r>
+  </si>
+  <si>
+    <t>I use arrows below to indicate relationships between one field and another:
+   A strong yellow arrow with a copy icon against it indicates that the lower item will normally be a direct copy of the earlier one.  You need therefore fill in the lower field only if you don't like the content of the earlier one.
+   A semi-transparent yellow arrow with a copy icon and a 'calculate' icon indicates that the converter normally attempts to work out a value for itself, but will take the value at the start of the arrow if the calculation fails.
+   Fill in the field at the end of the arrow if you want to override this action and force a different value in the lower field.
+   A white arrow with a 'calculate' icon indicates that the converter normally attempts to work out a value for itself, but will leave the field at the end of the arrow empty if the calculation fails.
+   As before, you can fill in the lower box to force your own value.</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Use of arrows</t>
+  </si>
+  <si>
+    <t>Caveats</t>
+  </si>
+  <si>
+    <t>#! Notes.</t>
+  </si>
+  <si>
+    <t>%Note#=</t>
   </si>
   <si>
     <r>
@@ -610,23 +611,55 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> – the processing doesn't use it.  I suggest you put the module name here, so that if this file gets separated from the rest of the data, you'll know what it belongs to.  (You can, of course, ignore the recommendation and / or add other things.)</t>
+      <t xml:space="preserve"> – the processing doesn't use it. Use this as you see fit.</t>
     </r>
   </si>
   <si>
-    <t>#! Text naming.  This information is used both in the STEPBible Bible chooser and (perhaps) on the copyright page.  If the English and vernacular details differ, both are used in some places.</t>
-  </si>
-  <si>
-    <t>#!</t>
-  </si>
-  <si>
-    <t>Controls certain aspects of the way the text can be handled.</t>
-  </si>
-  <si>
-    <t>Mainly for use in the Sword config file, but may also appear on the STEPBible copyright page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             Mainly for use in the Sword config file, but may also appear on the STEPBible copyright page.</t>
+    <t>The path to the metadata file.  Defaults to metadata.xml, but if you have a compelling reason to rename the file, give the name – eg myFile.conf – here.</t>
+  </si>
+  <si>
+    <t>The path to the licence file.  Defaults to license.xml, but if you have a compelling reason to rename the file, give the name – eg myFile.conf – here.</t>
+  </si>
+  <si>
+    <t>English Bible name as given by the translators.</t>
+  </si>
+  <si>
+    <t>English abbreviation as we want it on the Bible chooser.  If omitted, uses stepAbbreviationEnglishAsSupplied.</t>
+  </si>
+  <si>
+    <t>Vernacular Bible name as given by the translators.  If not filled in, takes the value from
+any external metadata file if available, otherwise uses the English version stepBibleNameEnglishAsSupplied.</t>
+  </si>
+  <si>
+    <t>Vernacular Bible name as we want it on the Bible chooser.  If omitted, uses stepBibleNameVernacularAsSupplied.</t>
+  </si>
+  <si>
+    <t>Vernacular abbreviation as given by the translators.  If not filled in, takes the value from
+any external metadata file if available, otherwise uses the English version stepBibleNameEnglishAsSupplied.</t>
+  </si>
+  <si>
+    <t>Vernacular abbreviation as we want it on the Bible chooser.  If omitted, uses stepAbbreviationVernacularAsSupplied.</t>
+  </si>
+  <si>
+    <t>A brief copyright notice.</t>
+  </si>
+  <si>
+    <t>Full name of the organisation which owns the text.</t>
+  </si>
+  <si>
+    <t>Website of the organisation which owns the text.</t>
+  </si>
+  <si>
+    <t>Template version 3.0</t>
+  </si>
+  <si>
+    <t>stepOurInternalIdentifierForTextOwner#=</t>
+  </si>
+  <si>
+    <t>stepOurInternalIdentifierForRepositoryOrganisation#=</t>
+  </si>
+  <si>
+    <t>Similar to stepOurInternalIdentifierForTextOwner, qv.  Used to determine the format of any external metadata which you may opt to pick up; and also in file names describing the repository organisation.</t>
   </si>
   <si>
     <r>
@@ -651,23 +684,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> override this, but I suggest you don't – the system can normally populate it for you.</t>
+      <t xml:space="preserve"> override this, but I suggest you don't – the system can normally populate it for you automatically from the language code. If you </t>
     </r>
-  </si>
-  <si>
-    <t>2-character language code.  Ususally deduced from the 3-char code which appears in the name of the folder containing the text you are working on.</t>
-  </si>
-  <si>
-    <t>Determines whether out-of-order verses are reported as errors or warnings.  User-supplied.  Defaults to Yes.</t>
-  </si>
-  <si>
-    <t>Says which Crosswire the scheme most closely follows.  Used on public texts only.  Must be one of the versification schemes supported by osis2mod.  User-supplied.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> From predefined list</t>
-  </si>
-  <si>
-    <t>What is says on the tin.  You probably want to accept the calculated value, and can therefore leave this blank.</t>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> opt to fill it in yourself, note that we don't tend to include details for languages which are very widely spoken.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -692,21 +731,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> made changes (cf calcModuleCreationDate, which is when we did something).  With DBL texts I calculate this if I can.</t>
-    </r>
-  </si>
-  <si>
-    <t>Needed in the Sword config file.  Defaults to Bible, but you can use Commentary where appropriate.</t>
-  </si>
-  <si>
-    <t>A canonical and minimsed version of the Bible name for use in the Bible chooser, baszed upon the English and vernacular details enteres above.  You'd normally accept the calcualted value here, but you can force a value if you need to.</t>
-  </si>
-  <si>
-    <t>For non-English texts, the name of language if available.  You can override if necessary.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Used where a text covers less than the full Protestant canon, to indicate coverage.  You can change this if you want to, but you probably </t>
+      <t xml:space="preserve"> made changes (cf calcModuleCreationDate, which is when </t>
     </r>
     <r>
       <rPr>
@@ -717,7 +742,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>don't</t>
+      <t>we</t>
     </r>
     <r>
       <rPr>
@@ -727,126 +752,184 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> want to, because the system will calculate it.</t>
+      <t xml:space="preserve"> did something).  With DBL texts I calculate this if I can.</t>
     </r>
   </si>
   <si>
-    <t>The calculated value draws together all of the above information in a standardised format (which is too complicated to describe here.  You can simply ignore everything done to date and enter your own value here – something which we are doing increasingly, but which is not easy to get right.</t>
-  </si>
-  <si>
-    <t>This appears as the About parameter in Sword configuration files, and on the copyright page as the detailed copyright information.  Typically it gives copyright and permitted usage details (drawn from the fields above), but on some texts we go beyond this, for instance with background information about the translation.  It also includes acknowledgements and, on public modules, outline information about any changes we may have applied during processing.</t>
-  </si>
-  <si>
-    <t>#! Information to appear on the STEPBible Bible chooser.</t>
-  </si>
-  <si>
-    <t>Any copyright information or usage limitations from the text supplier.  On DBL texts it may be possible to pick this up from the metadata file, but you should check.  It is also worth looking on the websites of text suppliers to see if they supply more detailed information.
-You can either put all of the details into this one field, or you can split out various special parts of it into the fields above, in which case the system can apply standard formatting to it, to make it easier to read.
-If using multiple lines, don't forget to put backslash at the end of all but the last.</t>
-  </si>
-  <si>
-    <t>As stipulated by supplier.  Eg Can’t use more than 500 verses from one book.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>As stipulated by supplier.  Eg Have to acknowledge.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>Occasionally extended descriptive information is supplied by the text supplier, or we may want to add comments of our own.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
-  </si>
-  <si>
-    <t>#! Textual copyright information.</t>
-  </si>
-  <si>
-    <t>Describing the text</t>
-  </si>
-  <si>
-    <t>Normally processing starts from eg USX if available.  This says to start from existing OSIS.  Required only other inputs are available in addition to OSIS.</t>
-  </si>
-  <si>
-    <t>#! Other settings you may require.  They are used as-is, and therefore need to be complete configuration statements eg myParm#=123.</t>
-  </si>
-  <si>
-    <t>#! There must be only one statement per box.  You can add more rows if you need them, but make sure you copy %AdditionalStatements#= or %AdditionalIncludes#= to each.</t>
-  </si>
-  <si>
-    <t>Any 'include' or 'includeIfExists' statements.</t>
-  </si>
-  <si>
-    <t>#! Processing mechanics.  Also affected by the section marked 'CONTROL' above.</t>
-  </si>
-  <si>
-    <t>swordTypeOfDocument#=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                           Details of the organisation which holds the text.  Often this will be the same as the owning organisation, in which case you can leave these entries blank.  But eg for DBL texts you will need details for DBL.</t>
-  </si>
-  <si>
+    <r>
+      <t xml:space="preserve">Needed in the Sword config file.  Defaults to </t>
+    </r>
     <r>
       <rPr>
-        <b/>
+        <i/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>I don't police things here: I make the assumption that if you fail to supply a value which the spreadsheet describes as being required , it will be because you are going to include, from here, other textual config files which make good the deficit.</t>
+      <t>Bible</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="11"/>
-        <color rgb="FF7030A0"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
+      <t xml:space="preserve">, but you can use </t>
     </r>
     <r>
       <rPr>
-        <b/>
+        <i/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-The converter automatically defaults as many parameters as possible, including many of these defined here.  However, if you supply a non-blank value here, it will override the default.
-A strong yellow arrow with a copy icon below indicates that the lower item will normally be a direct copy of the earlier one, and need therefore be filled in only if you want to override that value.
-A semi-transparent yellow arrow with a copy icon and a 'calculate' icon indicates that the converter normally works out a value for itself, but will take the value at the start of the arrow if the calculation fails.  Fill in the field at the end of the arrow if you want to override this and force a value.
-A white arrow with a 'calculate' icon indicates that the lower element is normally deduced from the earlier one, but is not a direct copy of it.  As before, you can fill in the lower box to force your own value.</t>
+      <t>Commentary</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
-        <b/>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FFFFFF00"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>CAVEATS</t>
+      <t xml:space="preserve"> where appropriate.</t>
+    </r>
+  </si>
+  <si>
+    <t>Any identifier supplied by the repository or text owner.  Recorded in admin comments only, to let us tie things together – it does not control the action of the processor, and is not actively used in the module.</t>
+  </si>
+  <si>
+    <t>On a few texts we include rights holder information in the Bible chooser, where someone other than the text owner has an interest in the text.  Enter something here if this is required.</t>
+  </si>
+  <si>
+    <t>A canonical and minimsed version of the Bible name for use in the Bible chooser, based upon the English and vernacular details entered above.  You'd normally accept the calculated value here, but you can force a value if you need to.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The calculated value draws together all of the above information in a standardised format (which is too complicated to describe here, and in any case seems quite frequently to be subject to change – see calcBibleChooserTextAssembly in *commonRoot.conf in the confugiration data folder).  You </t>
     </r>
     <r>
       <rPr>
-        <b/>
+        <u/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-Some of the 'Calculated' fields organise for other elements to be assembled into what we have adopted as a 'standard' order.  If you override these by supplying your own value, you will need to ensure that value contains the information we normally require in these fields, and that it is ordered appropriately.  Regrettably as things stand you can determine what the content and order should be only by reference to the various configuration files in the Resources section of the converter JAR, or by reference to the code, particularly that in ConfigData.kt.
-Similarly in a number of cases, fields are described as being potentially derived from DBL data where available.  Again, if you wish to find out how they are derived, you will need to have recourse to the built-in configutation files and the code.  You should be aware that deriving information from DBL is, in any case, somewhat of a black art, in that the DBL metadata doesn't seem to be documented anywhere, and people therefore apply their own interpretation in deciding which fields should be used for what purpose.  And then at the end of all this, increasingly we are deciding to override that data anyway.
-All of this means that you may well need to do one or two runs and examine the outputs until you achieve what you want.</t>
+      <t>can</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> simply ignore everything done to date and enter your own value here – something which we are doing increasingly, but which is not easy to get right.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As stipulated by supplier.  Eg </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Can’t use more than 500 verses from one book.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As stipulated by supplier.  Eg </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Have to acknowledge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.  This information ends up being used as part of the copyright statement.  If you give it here, I can format it neatly.  If that's not a great concern, you can simply include it as part of swordCopyrightStatement below.</t>
+    </r>
+  </si>
+  <si>
+    <t>Says whether STEPBible has added morphology to the text.  Used on the copyright page.</t>
+  </si>
+  <si>
+    <t>Says whether STEPBible has added Strongs to the text.  Used on the copyright page.</t>
+  </si>
+  <si>
+    <t>Says which Crosswire the scheme most closely follows.  Used on public texts only.  Must be one of the versification schemes supported by Crosswire's official osis2mod.  User-supplied.</t>
+  </si>
+  <si>
+    <t>Says whether this run should apply reversification or not.  Reversification is always applied on STEPBible texts, but (in contrast to our earlier intent) it no longer results in text being restructured in the conversion process – instead it retains its original structure, but is created in a way which makes it possible to reorder verses in the STEPBible application, for instance so that interlinear display will work.</t>
+  </si>
+  <si>
+    <t>Says whether we have vernacular format information which can be used, eg, for validating references.  This may also be useful in that it would enable us to use the correct formatting when we generate footnotes which contain references.  However, it is difficult to determine and record information about vernacular formats, and therefore it has not been used much.</t>
+  </si>
+  <si>
+    <t>Designates the format of any external metadata which you wish to pick up.  Copy of stepOurInternalIdentifierForRepositoryOrganisation if available, or failing that stepOurInternalIdentifierForTextOwner.</t>
+  </si>
+  <si>
+    <t>Ditto (provided their names follow the standard naming conventions) files giving details of the text owner, the text repository organisation, or the type of metadata which may be available.</t>
+  </si>
+  <si>
+    <t>Note that files in the Autoload area of the configuration data folder are automatically loaded, and you do not therefore need to mention them here.  Also .conf files co-located with this present file.</t>
+  </si>
+  <si>
+    <t>English abbreviation as given by the translators.  Normally taken from the name of the text root folder.</t>
+  </si>
+  <si>
+    <t>Used by permission.</t>
+  </si>
+  <si>
+    <t>{empty}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> yyyy[-mm-dd]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bible / Commentary</t>
+  </si>
+  <si>
+    <t>Bible</t>
   </si>
   <si>
     <r>
@@ -939,7 +1022,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> to supply a value (except where you know the value is available from third party metadata files, such as DBL's metadata.xml – a yellow border indicates where this could be the case).
+      <t xml:space="preserve"> to supply a value (except where you know the value will be available from third party metadata files, such as DBL's metadata.xml – a yellow border indicates where this could be the case).
 </t>
     </r>
     <r>
@@ -996,16 +1079,118 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Optional.
-   White:  These values are normally calculated but you can override them by providing your own values here if you wish (where there is no indication to the contrary).  In general, though, if it's white, you're unlikely to need to change it.</t>
+      <t xml:space="preserve">Optional.
+   White:  These values are normally calculated but you can override them by providing your own values here if you wish (where there is no indication to the contrary).  In general, though, if it's white, you're unlikely to need to change it.
+A few of the fields below are filled in with likely default values.
+Give the content as '{empty}' if you want to specify that the field has an empty value.  This is distingushed internally from you failing to specify a value at all.
+Single spaces </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>within</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> strings are respected.  Spaces at start and end, and multiple embedded spaces, are not.  Use '{space}' to force spaces where otherwise they might be ignored.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The converter automatically defaults as many parameters as possible, including some of those mentioned here.  It takes values from this file only if you have filled in a non-blank value.
+I don't police things here: I make the assumption that if you fail to supply a value which the spreadsheet describes as being required , it will be because you are going to include, from here, other textual config files which make good the deficit.</t>
+    </r>
+  </si>
+  <si>
+    <t>#!                                                        External metadata details.  Relevant only if you intend to pick up data automatically from metadata files supplied to you (presently possible only for DBL texts).  This tells the system which files to use, and what format they are in.</t>
+  </si>
+  <si>
+    <t>Mainly for use in the Sword config file, but may also appear on the STEPBible copyright page, along with much fuller details (discussed below).</t>
+  </si>
+  <si>
+    <t>#! Organisational details.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                     Details of the organisation which holds the text.  Often this will be the same as the owning organisation, in which case you can leave these entries blank.  But eg for DBL texts you will need details for DBL.</t>
+  </si>
+  <si>
+    <t>#! Information to appear on the STEPBible Bible chooser.  This needs to be comprehensive but concise and to follow a standard pattern as far as possible.  The automated processing usually does a reasonable job, but you can override if necessary.</t>
+  </si>
+  <si>
+    <t>#! Copyright details and controls based on copyright.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Note that you can't do a public build if the text is marked as copyright.</t>
+  </si>
+  <si>
+    <t>Should text be available online only?  If you add '_online' to the end of the name of the text's root folder, this is taken as yes.  Alternatively you can specify it here.</t>
+  </si>
+  <si>
+    <t>The information in this section simply feeds into calcAboutAssembly.  If you split it out into the separate boxes as bet you can, calcAboutAssembly will assemble it into a 'standard' order and format.  If that's awkward, you can simply put all the details into swordCopyrightStatement.</t>
+  </si>
+  <si>
+    <t>This can be any string which identifies the text owner, and which is suitable for use
+in file names and in Kotlin code.  It serves two purposes.  First, the processing will look for facilities to pre-process input from this text owner (presently useful only for Biblica, who tend to have systematic idiosyncrasies in their text).  And second it provides a means of systematically naming configuration files containing information about this text supplier.  Again, for instance, we do make provision for picking up Biblica-related configuration information automatically.  (It's not a problem if, in fact, we do not have files related to this particular text owner.)</t>
+  </si>
+  <si>
+    <t>Determines whether out-of-order verses are reported as errors.  Defaults to Yes meaning report as errors.  If set to No, they are reported as warnings.  (Normally out-of-order verses are likely to be errors, but we've come across a very few texts where verses were deliberately positioned in the 'wrong' order.)</t>
+  </si>
+  <si>
+    <t>Official abbreviated name of the organisation which owns the text.  Uses full name if abbreviated name is not available.</t>
+  </si>
+  <si>
+    <t>Official abbreviated name of organisation which holds the text.  Uses full name if abbreviated name is not available.</t>
+  </si>
+  <si>
+    <t>swordCopyrightStatement#=</t>
+  </si>
+  <si>
+    <t>Fuller copyright details for use on STEPBible copyright page.</t>
+  </si>
+  <si>
+    <t>Used in the Sword config file.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1134,8 +1319,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1220,37 +1413,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="31">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1422,14 +1597,135 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFF00"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFF00"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFF00"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFF00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1437,16 +1733,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1490,172 +1808,256 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1688,13 +2090,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3309938</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3700463</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1710,8 +2112,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3576638" y="6162675"/>
-          <a:ext cx="390525" cy="228599"/>
+          <a:off x="3652838" y="38433375"/>
+          <a:ext cx="390525" cy="609599"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -1763,13 +2165,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2133600</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2524125</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1838,13 +2240,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3278982</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3669507</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1913,13 +2315,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1990,13 +2392,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3278982</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>200024</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3669507</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2065,13 +2467,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1019175</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2142,13 +2544,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3278982</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3669507</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2217,13 +2619,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3309938</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3700463</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2288,86 +2690,11 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3495675</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3886200</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Arrow: Down 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D25AE172-A4E3-4053-8E31-3220DBF2B800}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3762375" y="16811625"/>
-          <a:ext cx="390525" cy="228599"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
-            <a:srgbClr val="000000">
-              <a:alpha val="99000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>56173</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="405432" cy="2419351"/>
@@ -2421,7 +2748,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>ENGLISH</a:t>
+            <a:t>ENGLISH NAMING</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2432,7 +2759,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>56172</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="405432" cy="3009900"/>
@@ -2486,7 +2813,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>VERNACULAR</a:t>
+            <a:t>VERNACULAR NAMING</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2497,13 +2824,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3733800</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3962400</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2533,7 +2860,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4000500" y="9963150"/>
+          <a:off x="4076700" y="10534650"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2546,15 +2873,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3714750</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>3695700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3943350</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>3924300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2583,7 +2910,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3981450" y="11372850"/>
+          <a:off x="4038600" y="11963400"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2597,14 +2924,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3724275</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3952875</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>438150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2633,7 +2960,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3990975" y="6905625"/>
+          <a:off x="4067175" y="38452425"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2646,15 +2973,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2000250</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>2505075</xdr:colOff>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2228850</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>2733675</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2683,7 +3010,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2266950" y="9858375"/>
+          <a:off x="2847975" y="38414325"/>
           <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2697,13 +3024,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1600200</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2747,13 +3074,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1171575</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2797,13 +3124,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1600200</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>266700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1828800</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2847,13 +3174,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1171575</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1400175</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>523875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2897,13 +3224,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3676650</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>533400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2947,14 +3274,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3714750</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3943350</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>485775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2993,314 +3320,14 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3895725</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>4124325</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Picture 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C65C9850-4AAB-4458-9561-6F8AF1AD61A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4162425" y="16973550"/>
-          <a:ext cx="228600" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1123950</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="Arrow: Down 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68673E3-398C-49EE-9413-676C4C747744}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1000125" y="24526874"/>
-          <a:ext cx="390525" cy="3476625"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
-            <a:srgbClr val="000000">
-              <a:alpha val="99000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A3C9A2-39D0-4A6B-814B-ACCC29824716}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1409700" y="22517100"/>
-          <a:ext cx="228600" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="Arrow: Down 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9697353-3D28-45C8-A598-4DFA8104E35C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="542925" y="24117299"/>
-          <a:ext cx="390525" cy="3533776"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
-            <a:srgbClr val="000000">
-              <a:alpha val="99000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>828675</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Picture 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791B1F30-9D2F-4818-AD95-F7EFBC374275}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="866775" y="22269450"/>
-          <a:ext cx="228600" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="405432" cy="1838328"/>
+    <xdr:ext cx="657225" cy="1304926"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="36" name="TextBox 35">
@@ -3314,8 +3341,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="-402122" y="20518922"/>
-          <a:ext cx="1838328" cy="405432"/>
+          <a:off x="38100" y="18792824"/>
+          <a:ext cx="1304926" cy="657225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3338,13 +3365,24 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
-          <a:spAutoFit/>
+          <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1">
+            <a:rPr lang="en-GB" sz="1500" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>COPYRIGHT</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1500" b="1">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -3358,12 +3396,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38101</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>95248</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="405432" cy="1266825"/>
+    <xdr:ext cx="1628777" cy="1457326"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="37" name="TextBox 36">
@@ -3377,8 +3415,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="-125896" y="19585471"/>
-          <a:ext cx="1266825" cy="405432"/>
+          <a:off x="85727" y="20326347"/>
+          <a:ext cx="1457326" cy="1628777"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3401,7 +3439,7 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
-          <a:spAutoFit/>
+          <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
@@ -3412,7 +3450,18 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>BRIEF</a:t>
+            <a:t>BRIEF COPYRIGHT</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>DETAILS</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3423,10 +3472,10 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>15749</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="405432" cy="2933703"/>
+    <xdr:ext cx="405432" cy="3228978"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="38" name="TextBox 37">
@@ -3440,8 +3489,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="-981687" y="21885760"/>
-          <a:ext cx="2933703" cy="405432"/>
+          <a:off x="-1053124" y="24014597"/>
+          <a:ext cx="3228978" cy="405432"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3486,10 +3535,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>120524</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>28577</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="405432" cy="1085850"/>
+    <xdr:ext cx="405432" cy="1524001"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="39" name="TextBox 38">
@@ -3503,8 +3552,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="-86335" y="27486461"/>
-          <a:ext cx="1085850" cy="405432"/>
+          <a:off x="-229211" y="26829236"/>
+          <a:ext cx="1524001" cy="405432"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3538,7 +3587,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>REPO</a:t>
+            <a:t>REPOSITORY</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3549,13 +3598,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>209549</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3624,13 +3673,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>828675</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>209548</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3699,13 +3748,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>866775</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>200024</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3774,13 +3823,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1714500</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3849,13 +3898,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1800225</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2190750</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3924,14 +3973,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>419100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3974,13 +4023,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>990600</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4024,13 +4073,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1438275</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>419100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4074,13 +4123,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1676400</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>146</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4124,13 +4173,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2143125</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2371725</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>400050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4174,14 +4223,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>209551</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4196,8 +4245,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="571500" y="41786175"/>
-          <a:ext cx="390525" cy="2943226"/>
+          <a:off x="647700" y="22602825"/>
+          <a:ext cx="390525" cy="6477000"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -4249,13 +4298,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4298,15 +4347,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:colOff>1133475</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4321,8 +4370,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1038225" y="42710100"/>
-          <a:ext cx="390525" cy="2009775"/>
+          <a:off x="1085850" y="23526751"/>
+          <a:ext cx="390525" cy="5562600"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -4374,13 +4423,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1123950</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4424,14 +4473,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1171575</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1562100</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4446,8 +4495,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1438275" y="42824400"/>
-          <a:ext cx="390525" cy="733425"/>
+          <a:off x="1514475" y="24422100"/>
+          <a:ext cx="390525" cy="4667250"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -4499,13 +4548,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1752600</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>389296</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4547,18 +4596,18 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>117776</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="405432" cy="5038727"/>
+    <xdr:ext cx="468077" cy="971552"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="TextBox 60">
+        <xdr:cNvPr id="62" name="TextBox 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47792150-85CF-4A6F-A08A-ADBD4685AF90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08433BE9-7051-42BF-A145-73F88E43C9E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4566,8 +4615,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="-2049948" y="43864698"/>
-          <a:ext cx="5038727" cy="405432"/>
+          <a:off x="75589" y="27893288"/>
+          <a:ext cx="971552" cy="468077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4596,83 +4645,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>SUPPLIED COPYRIGHT</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> INFORMATION</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="2000" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>74125</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>9526</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1031629" cy="971552"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="TextBox 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08433BE9-7051-42BF-A145-73F88E43C9E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="237514" y="46794862"/>
-          <a:ext cx="971552" cy="1031629"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1">
+            <a:rPr lang="en-GB" sz="1200" b="1">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -4680,7 +4653,7 @@
             <a:t>OUR</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -4692,80 +4665,17 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="405432" cy="1428749"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="TextBox 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97926A2-4C4D-469E-A7DB-38F73EF3D1A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="-244959" y="48546234"/>
-          <a:ext cx="1428749" cy="405432"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="2000" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>COMBINED</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1647825</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2038350</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4834,13 +4744,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2085975</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2476500</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4909,13 +4819,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2400300</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2628900</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>189271</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4959,13 +4869,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2552700</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2943225</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5034,13 +4944,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2876550</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3105150</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>170221</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5084,13 +4994,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2009775</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2238375</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>341671</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5122,6 +5032,645 @@
         <a:xfrm>
           <a:off x="2276475" y="44672250"/>
           <a:ext cx="228600" cy="189271"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Arrow: Down 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{021C272B-7FDC-4427-B63B-D77344B08F8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="581025" y="26612850"/>
+          <a:ext cx="390525" cy="1952625"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="99000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>588168</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>816768</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0884FE6-F462-4596-A96D-1DBA50E99359}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="931068" y="26670000"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>847725</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1238250</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Arrow: Down 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82308256-C2C4-47B9-9070-DD4EBDE98B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1190625" y="33385124"/>
+          <a:ext cx="390525" cy="4991100"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="99000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1226343</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1454943</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>476250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39DB9D16-EF05-4AFB-BC9A-CFBB7E424204}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1569243" y="33489900"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="405432" cy="5343528"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="TextBox 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94748307-EB1E-46CC-B035-E989E638BCD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="-2126148" y="24186048"/>
+          <a:ext cx="5343528" cy="405432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SUPPLIED COPYRIGHT</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> INFORMATION</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="405432" cy="1533525"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6611D317-7072-4A3D-81AB-2DA4B6252C7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="-221147" y="29529572"/>
+          <a:ext cx="1533525" cy="405432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>COMBINED</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2847975</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3238500</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Arrow: Down 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E4DE994-D541-4339-BE6A-147F076CF816}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3190875" y="32061150"/>
+          <a:ext cx="390525" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="99000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3267075</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3495675</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83B482D1-57FE-4428-B218-7597E5E48F42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3609975" y="32042100"/>
+          <a:ext cx="228600" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2762250</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3152775</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Arrow: Down 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6DD94FB-19E8-46E2-92E8-EA38C2600716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3105150" y="35747325"/>
+          <a:ext cx="390525" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="2700000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="99000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3181350</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3409950</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{913A3E09-667C-45C6-A904-42C2F4801CA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3524250" y="35728275"/>
+          <a:ext cx="228600" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5430,2009 +5979,1991 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418B6D20-05C6-40BC-A9B4-171C309EC83D}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="2" style="10" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="2" style="10" customWidth="1"/>
     <col min="3" max="3" width="68.28515625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="87.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="87.85546875" style="39" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="80.28515625" style="12" customWidth="1"/>
     <col min="7" max="7" width="2.7109375" style="12" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="57" customFormat="1" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="58"/>
-    </row>
-    <row r="2" spans="1:7" s="57" customFormat="1" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="58"/>
-    </row>
-    <row r="3" spans="1:7" s="57" customFormat="1" ht="168" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="58"/>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="33" customFormat="1" ht="351.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:8" s="36" customFormat="1" ht="149.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="35"/>
+    </row>
+    <row r="3" spans="1:8" s="36" customFormat="1" ht="168" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:8" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="7"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="88"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="87"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="87"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" s="21" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="82"/>
+    </row>
+    <row r="11" spans="1:8" s="16" customFormat="1" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
-      <c r="B12" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="74"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="75"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="76"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="75"/>
+    </row>
+    <row r="15" spans="1:8" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="76"/>
+      <c r="C15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="75"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="75"/>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="76"/>
+      <c r="C17" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="75"/>
+    </row>
+    <row r="18" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="76"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="75"/>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="76"/>
+      <c r="C19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="75"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="16"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="76"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="75"/>
+    </row>
+    <row r="21" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" s="21" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="75"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="76"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="23"/>
+      <c r="D22" s="45"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F22" s="27"/>
+      <c r="G22" s="75"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
-      <c r="B23" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="54"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="76"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="75"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="54"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="76"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="75"/>
+    </row>
+    <row r="25" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="54"/>
-    </row>
-    <row r="26" spans="1:7" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="76"/>
+      <c r="C25" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="40"/>
+      <c r="E25" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="75"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="54"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="76"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="75"/>
+    </row>
+    <row r="27" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="54"/>
-    </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="76"/>
+      <c r="C27" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="75"/>
+    </row>
+    <row r="28" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="G28" s="54"/>
-    </row>
-    <row r="29" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="76"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="75"/>
+    </row>
+    <row r="29" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="54"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="40"/>
+      <c r="E29" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="54"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="76"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="75"/>
+    </row>
+    <row r="31" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="54"/>
-    </row>
-    <row r="32" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="76"/>
+      <c r="C31" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="43"/>
+      <c r="E31" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="75"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="54"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="76"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="75"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="54"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="54"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="77"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82"/>
+    </row>
+    <row r="34" spans="1:7" s="16" customFormat="1" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="54"/>
-    </row>
-    <row r="36" spans="1:7" s="21" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B35" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="69"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="73"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="G36" s="54"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="75"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="54"/>
-    </row>
-    <row r="38" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B37" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="48"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="87"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="54"/>
-    </row>
-    <row r="39" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="86"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="87"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="54"/>
-    </row>
-    <row r="40" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B39" s="76"/>
+      <c r="C39" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="87"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="G40" s="54"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="76"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="87"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="54"/>
-    </row>
-    <row r="42" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B41" s="76"/>
+      <c r="C41" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="49"/>
+      <c r="E41" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="87"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F42" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="54"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="76"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="87"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="54"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="76"/>
+      <c r="C43" s="67"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="87"/>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="54"/>
-    </row>
-    <row r="45" spans="1:7" s="21" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-    </row>
-    <row r="46" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D44" s="48"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="87"/>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+      <c r="B45" s="86"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="87"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
-      <c r="B46" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-    </row>
-    <row r="47" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="33"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="B46" s="76"/>
+      <c r="C46" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G46" s="87"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="87"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
-      <c r="B48" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="60"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="16"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="87"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="14"/>
-      <c r="B49" s="62"/>
-      <c r="C49" s="63"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="16"/>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="76"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="87"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="14"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="29"/>
-      <c r="E50" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="G50" s="16"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="40"/>
+      <c r="E50" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="87"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="16"/>
-    </row>
-    <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="76"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="87"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="16"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="67"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="87"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="16"/>
-    </row>
-    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B53" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="48"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="87"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="G54" s="16"/>
+      <c r="B54" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="56"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="87"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="16"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
-      <c r="B57" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="60"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="16"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="86"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="87"/>
+    </row>
+    <row r="56" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="76"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="87"/>
+    </row>
+    <row r="57" spans="1:7" s="28" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="10"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="40"/>
+      <c r="E57" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G57" s="75"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
-      <c r="B58" s="62"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="16"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="76"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="87"/>
+    </row>
+    <row r="59" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="29"/>
-      <c r="E59" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F59" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="16"/>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="76"/>
+      <c r="C59" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="40"/>
+      <c r="E59" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G59" s="87"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="16"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="76"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="87"/>
+    </row>
+    <row r="61" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F61" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="G61" s="16"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="76"/>
+      <c r="C61" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="40"/>
+      <c r="E61" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" s="87"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="16"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="76"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="87"/>
+    </row>
+    <row r="63" spans="1:7" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="19"/>
-      <c r="E63" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="G63" s="16"/>
+      <c r="B63" s="76"/>
+      <c r="C63" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D63" s="42"/>
+      <c r="E63" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" s="87"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="45"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="16"/>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="76"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="87"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+      <c r="B65" s="76"/>
+      <c r="C65" s="67"/>
+      <c r="D65" s="64"/>
+      <c r="E65" s="65"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="87"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
-      <c r="B66" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="60"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="16"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="76"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="23"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="87"/>
+    </row>
+    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14"/>
-      <c r="B67" s="62"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="16"/>
-    </row>
-    <row r="68" spans="1:7" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="76"/>
+      <c r="C67" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="40"/>
+      <c r="E67" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G67" s="87"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="14"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="D68" s="59"/>
-      <c r="E68" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F68" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="16"/>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="76"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="87"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="14"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="16"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="76"/>
+      <c r="C69" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" s="40"/>
+      <c r="E69" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G69" s="87"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" s="36"/>
-      <c r="E70" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F70" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="G70" s="16"/>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="76"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="87"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="14"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="16"/>
-    </row>
-    <row r="72" spans="1:7" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="76"/>
+      <c r="C71" s="89"/>
+      <c r="D71" s="91"/>
+      <c r="E71" s="92"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="87"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="14"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="36"/>
-      <c r="E72" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F72" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="G72" s="16"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="76"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="87"/>
+    </row>
+    <row r="73" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A73" s="14"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="16"/>
-    </row>
-    <row r="74" spans="1:7" s="21" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="B73" s="76"/>
+      <c r="C73" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" s="53"/>
+      <c r="E73" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="G73" s="87"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="14"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="19"/>
-      <c r="E74" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="G74" s="16"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="76"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="87"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="16"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="34"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="77"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="80"/>
+      <c r="F75" s="81"/>
+      <c r="G75" s="82"/>
+    </row>
+    <row r="76" spans="1:7" s="16" customFormat="1" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="15"/>
+      <c r="B76" s="58"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="61"/>
+      <c r="F76" s="62"/>
+      <c r="G76" s="62"/>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" s="69"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="71"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="73"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
-      <c r="B78" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="D78" s="60"/>
-      <c r="E78" s="43"/>
-      <c r="F78" s="47"/>
-      <c r="G78" s="16"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="66"/>
+      <c r="G78" s="87"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="63"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="44"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="16"/>
-    </row>
-    <row r="80" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D79" s="48"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="87"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D80" s="19"/>
-      <c r="E80" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="F80" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="G80" s="16"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="86"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="87"/>
+    </row>
+    <row r="81" spans="1:7" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="14"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="39"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="16"/>
-    </row>
-    <row r="82" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="76"/>
+      <c r="C81" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="51"/>
+      <c r="E81" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F81" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G81" s="87"/>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="14"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D82" s="19"/>
-      <c r="E82" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="F82" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G82" s="16"/>
-    </row>
-    <row r="83" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="18"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="45"/>
-      <c r="F83" s="49"/>
-      <c r="G83" s="16"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="76"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="87"/>
+    </row>
+    <row r="83" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="14"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="52"/>
+      <c r="E83" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F83" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="G83" s="87"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="14"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-    </row>
-    <row r="85" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="20"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
+      <c r="B84" s="76"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="56"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="87"/>
+    </row>
+    <row r="85" spans="1:7" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="14"/>
+      <c r="B85" s="76"/>
+      <c r="C85" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="52"/>
+      <c r="E85" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="G85" s="87"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
-      <c r="B86" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" s="34"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="76"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="87"/>
+    </row>
+    <row r="87" spans="1:7" s="16" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-    </row>
-    <row r="88" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B87" s="76"/>
+      <c r="C87" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="40"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="G87" s="87"/>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D88" s="28"/>
-      <c r="E88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F88" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G88" s="16"/>
+      <c r="B88" s="76"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="87"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-    </row>
-    <row r="90" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B89" s="74"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="64"/>
+      <c r="E89" s="65"/>
+      <c r="F89" s="66"/>
+      <c r="G89" s="87"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D90" s="28"/>
-      <c r="E90" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="G90" s="16"/>
-    </row>
-    <row r="91" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D90" s="48"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="87"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
-    </row>
-    <row r="92" spans="1:7" s="21" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="86"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="56"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="87"/>
+    </row>
+    <row r="92" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D92" s="65"/>
-      <c r="E92" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="G92" s="16"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="40"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="87"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="16"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
-    </row>
-    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B93" s="76"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="87"/>
+    </row>
+    <row r="94" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D94" s="19"/>
-      <c r="E94" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F94" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G94" s="16"/>
+      <c r="B94" s="76"/>
+      <c r="C94" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="40"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G94" s="87"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="14"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="16"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-    </row>
-    <row r="96" spans="1:7" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B95" s="76"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="87"/>
+    </row>
+    <row r="96" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="14"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D96" s="19"/>
-      <c r="E96" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G96" s="16"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="14"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="16"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="16"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
-      <c r="B99" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C99" s="34"/>
-      <c r="D99" s="16"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="16"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="16"/>
-      <c r="G100" s="16"/>
-    </row>
-    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B96" s="76"/>
+      <c r="C96" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" s="40"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="G96" s="87"/>
+    </row>
+    <row r="97" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="76"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="87"/>
+    </row>
+    <row r="98" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="14"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="78"/>
+      <c r="D98" s="79"/>
+      <c r="E98" s="80"/>
+      <c r="F98" s="81"/>
+      <c r="G98" s="82"/>
+    </row>
+    <row r="99" spans="1:7" s="16" customFormat="1" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="58"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="60"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="62"/>
+      <c r="G99" s="62"/>
+    </row>
+    <row r="100" spans="1:7" s="14" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C100" s="17"/>
+      <c r="D100" s="55"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="18"/>
+    </row>
+    <row r="101" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A101" s="14"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D101" s="28"/>
-      <c r="E101" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F101" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="G101" s="16"/>
+      <c r="B101" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" s="69"/>
+      <c r="D101" s="70"/>
+      <c r="E101" s="71"/>
+      <c r="F101" s="72"/>
+      <c r="G101" s="88"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="14"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="15"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="16"/>
-    </row>
-    <row r="103" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B103" s="18"/>
-      <c r="C103" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D103" s="28"/>
-      <c r="E103" s="17" t="s">
+      <c r="B102" s="76"/>
+      <c r="C102" s="67"/>
+      <c r="D102" s="64"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="87"/>
+    </row>
+    <row r="103" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A103" s="14"/>
+      <c r="B103" s="76"/>
+      <c r="C103" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="40"/>
+      <c r="E103" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="F103" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G103" s="16"/>
-    </row>
-    <row r="104" spans="1:7" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="10"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="53"/>
-      <c r="D104" s="54"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="54"/>
-      <c r="G104" s="54"/>
-    </row>
-    <row r="105" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D105" s="28"/>
-      <c r="E105" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F105" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G105" s="16"/>
-    </row>
-    <row r="106" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F103" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="G103" s="87"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="14"/>
+      <c r="B104" s="76"/>
+      <c r="C104" s="67"/>
+      <c r="D104" s="64"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="87"/>
+    </row>
+    <row r="105" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B105" s="76"/>
+      <c r="C105" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="40"/>
+      <c r="E105" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="F105" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="G105" s="87"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="14"/>
-      <c r="B106" s="18"/>
-      <c r="C106" s="15"/>
-      <c r="D106" s="16"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="16"/>
-      <c r="G106" s="16"/>
-    </row>
-    <row r="107" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="76"/>
+      <c r="C106" s="67"/>
+      <c r="D106" s="64"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="66"/>
+      <c r="G106" s="87"/>
+    </row>
+    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="14"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D107" s="27"/>
-      <c r="E107" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F107" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="G107" s="16"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B107" s="76"/>
+      <c r="C107" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="40"/>
+      <c r="E107" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="F107" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="G107" s="87"/>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="14"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="15"/>
-      <c r="D108" s="16"/>
-      <c r="E108" s="17"/>
-      <c r="F108" s="16"/>
-      <c r="G108" s="16"/>
-    </row>
-    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="14"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D109" s="26"/>
-      <c r="E109" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F109" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="G109" s="16"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B108" s="77"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="79"/>
+      <c r="E108" s="80"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="82"/>
+    </row>
+    <row r="109" spans="1:7" s="16" customFormat="1" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="15"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="17"/>
+      <c r="D109" s="85"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+    </row>
+    <row r="110" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14"/>
-      <c r="B110" s="18"/>
-      <c r="C110" s="15"/>
-      <c r="D110" s="16"/>
-      <c r="E110" s="17"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
-    </row>
-    <row r="111" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B110" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="69"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="71"/>
+      <c r="F110" s="72"/>
+      <c r="G110" s="88"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="14"/>
-      <c r="B111" s="18"/>
-      <c r="C111" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D111" s="19"/>
-      <c r="E111" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F111" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="G111" s="16"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="76"/>
+      <c r="C111" s="67"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="65"/>
+      <c r="F111" s="66"/>
+      <c r="G111" s="87"/>
+    </row>
+    <row r="112" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="14"/>
-      <c r="B112" s="18"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="16"/>
-      <c r="E112" s="17"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="16"/>
-    </row>
-    <row r="113" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="20"/>
-      <c r="C113" s="22"/>
-      <c r="D113" s="23"/>
-      <c r="E113" s="24"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B112" s="76"/>
+      <c r="C112" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="53"/>
+      <c r="E112" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F112" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="G112" s="87"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="14"/>
+      <c r="B113" s="76"/>
+      <c r="C113" s="67"/>
+      <c r="D113" s="64"/>
+      <c r="E113" s="65"/>
+      <c r="F113" s="66"/>
+      <c r="G113" s="87"/>
+    </row>
+    <row r="114" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
-      <c r="B114" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C114" s="34"/>
-      <c r="D114" s="16"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="16"/>
-      <c r="G114" s="16"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B114" s="76"/>
+      <c r="C114" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="53"/>
+      <c r="E114" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="G114" s="87"/>
+    </row>
+    <row r="115" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="14"/>
-      <c r="B115" s="18"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="17"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="16"/>
-    </row>
-    <row r="116" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B115" s="76"/>
+      <c r="C115" s="67"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="66"/>
+      <c r="G115" s="87"/>
+    </row>
+    <row r="116" spans="1:7" s="16" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="14"/>
-      <c r="B116" s="18"/>
-      <c r="C116" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D116" s="19"/>
-      <c r="E116" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F116" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G116" s="16"/>
+      <c r="B116" s="76"/>
+      <c r="C116" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="54"/>
+      <c r="E116" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="F116" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" s="87"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="14"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="15"/>
-      <c r="D117" s="16"/>
-      <c r="E117" s="17"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="16"/>
-    </row>
-    <row r="118" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B117" s="76"/>
+      <c r="C117" s="67"/>
+      <c r="D117" s="64"/>
+      <c r="E117" s="65"/>
+      <c r="F117" s="66"/>
+      <c r="G117" s="87"/>
+    </row>
+    <row r="118" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
-      <c r="B118" s="18"/>
-      <c r="C118" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D118" s="28"/>
-      <c r="E118" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F118" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="G118" s="16"/>
+      <c r="B118" s="76"/>
+      <c r="C118" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="40"/>
+      <c r="E118" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="G118" s="87"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="14"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="15"/>
-      <c r="D119" s="16"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="16"/>
-      <c r="G119" s="16"/>
-    </row>
-    <row r="120" spans="1:7" s="21" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B119" s="76"/>
+      <c r="C119" s="67"/>
+      <c r="D119" s="64"/>
+      <c r="E119" s="65"/>
+      <c r="F119" s="66"/>
+      <c r="G119" s="87"/>
+    </row>
+    <row r="120" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="14"/>
-      <c r="B120" s="18"/>
-      <c r="C120" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D120" s="28"/>
-      <c r="E120" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F120" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G120" s="16"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B120" s="76"/>
+      <c r="C120" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120" s="40"/>
+      <c r="E120" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="F120" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="87"/>
+    </row>
+    <row r="121" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14"/>
-      <c r="B121" s="18"/>
-      <c r="C121" s="15"/>
-      <c r="D121" s="16"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="16"/>
-      <c r="G121" s="16"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="14"/>
-      <c r="B122" s="18"/>
-      <c r="C122" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D122" s="28"/>
-      <c r="E122" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F122" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="G122" s="16"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B121" s="77"/>
+      <c r="C121" s="78"/>
+      <c r="D121" s="79"/>
+      <c r="E121" s="80"/>
+      <c r="F121" s="81"/>
+      <c r="G121" s="82"/>
+    </row>
+    <row r="122" spans="1:7" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="123" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14"/>
-      <c r="B123" s="18"/>
-      <c r="C123" s="15"/>
-      <c r="D123" s="16"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="16"/>
-      <c r="G123" s="16"/>
-    </row>
-    <row r="124" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B123" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" s="69"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="71"/>
+      <c r="F123" s="72"/>
+      <c r="G123" s="88"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="14"/>
-      <c r="B124" s="18"/>
-      <c r="C124" s="15" t="s">
+      <c r="B124" s="76"/>
+      <c r="C124" s="67"/>
+      <c r="D124" s="64"/>
+      <c r="E124" s="65"/>
+      <c r="F124" s="66"/>
+      <c r="G124" s="87"/>
+    </row>
+    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="14"/>
+      <c r="B125" s="76"/>
+      <c r="C125" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" s="53"/>
+      <c r="E125" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F125" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D124" s="28"/>
-      <c r="E124" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F124" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G124" s="16"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="14"/>
-      <c r="B125" s="18"/>
-      <c r="C125" s="15"/>
-      <c r="D125" s="16"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="16"/>
-      <c r="G125" s="16"/>
-    </row>
-    <row r="126" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="G125" s="87"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="14"/>
-      <c r="B126" s="18"/>
-      <c r="C126" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="D126" s="28"/>
-      <c r="E126" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F126" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G126" s="16"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="14"/>
-      <c r="B127" s="18"/>
-      <c r="C127" s="15"/>
-      <c r="D127" s="16"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="16"/>
-      <c r="G127" s="16"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B126" s="76"/>
+      <c r="C126" s="67"/>
+      <c r="D126" s="64"/>
+      <c r="E126" s="65"/>
+      <c r="F126" s="66"/>
+      <c r="G126" s="87"/>
+    </row>
+    <row r="127" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B127" s="76"/>
+      <c r="C127" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="53"/>
+      <c r="E127" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F127" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127" s="87"/>
+    </row>
+    <row r="128" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="10"/>
+      <c r="B128" s="90"/>
+      <c r="C128" s="89"/>
+      <c r="D128" s="91"/>
+      <c r="E128" s="92"/>
+      <c r="F128" s="84"/>
+      <c r="G128" s="75"/>
+    </row>
+    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
-      <c r="B129" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C129" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="D129" s="16"/>
-      <c r="E129" s="17"/>
-      <c r="F129" s="16"/>
-      <c r="G129" s="16"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B129" s="76"/>
+      <c r="C129" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D129" s="53"/>
+      <c r="E129" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F129" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="G129" s="87"/>
+    </row>
+    <row r="130" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="14"/>
-      <c r="B130" s="33"/>
-      <c r="C130" s="34"/>
-      <c r="D130" s="16"/>
-      <c r="E130" s="17"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="16"/>
-    </row>
-    <row r="131" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="18"/>
-      <c r="C131" s="38"/>
-      <c r="D131" s="60"/>
-      <c r="E131" s="43"/>
-      <c r="F131" s="47"/>
-      <c r="G131" s="16"/>
-    </row>
-    <row r="132" spans="1:7" s="51" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A132" s="10"/>
-      <c r="B132" s="52"/>
-      <c r="C132" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D132" s="19"/>
-      <c r="E132" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F132" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="G132" s="54"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B130" s="76"/>
+      <c r="C130" s="67"/>
+      <c r="D130" s="64"/>
+      <c r="E130" s="65"/>
+      <c r="F130" s="66"/>
+      <c r="G130" s="87"/>
+    </row>
+    <row r="131" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="14"/>
+      <c r="B131" s="76"/>
+      <c r="C131" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="D131" s="42"/>
+      <c r="E131" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="F131" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="G131" s="87"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="14"/>
+      <c r="B132" s="76"/>
+      <c r="C132" s="67"/>
+      <c r="D132" s="64"/>
+      <c r="E132" s="65"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="87"/>
+    </row>
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="14"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="39"/>
-      <c r="D133" s="37"/>
-      <c r="E133" s="44"/>
-      <c r="F133" s="48"/>
-      <c r="G133" s="16"/>
-    </row>
-    <row r="134" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B133" s="76"/>
+      <c r="C133" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="D133" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E133" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="F133" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="G133" s="87"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="14"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D134" s="19"/>
-      <c r="E134" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F134" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="G134" s="16"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B134" s="76"/>
+      <c r="C134" s="67"/>
+      <c r="D134" s="64"/>
+      <c r="E134" s="65"/>
+      <c r="F134" s="66"/>
+      <c r="G134" s="87"/>
+    </row>
+    <row r="135" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="14"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="37"/>
-      <c r="E135" s="44"/>
-      <c r="F135" s="48"/>
-      <c r="G135" s="16"/>
-    </row>
-    <row r="136" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B135" s="76"/>
+      <c r="C135" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D135" s="40"/>
+      <c r="E135" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F135" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="G135" s="87"/>
+    </row>
+    <row r="136" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="14"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D136" s="19"/>
-      <c r="E136" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F136" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G136" s="16"/>
-    </row>
-    <row r="137" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="14"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="39"/>
-      <c r="D137" s="37"/>
-      <c r="E137" s="44"/>
-      <c r="F137" s="48"/>
-      <c r="G137" s="16"/>
-    </row>
-    <row r="138" spans="1:7" ht="150.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="77"/>
+      <c r="C136" s="78"/>
+      <c r="D136" s="79"/>
+      <c r="E136" s="80"/>
+      <c r="F136" s="81"/>
+      <c r="G136" s="82"/>
+    </row>
+    <row r="137" spans="1:7" s="16" customFormat="1" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="15"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="17"/>
+      <c r="D137" s="85"/>
+      <c r="E137" s="19"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+    </row>
+    <row r="138" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A138" s="14"/>
-      <c r="B138" s="18"/>
-      <c r="C138" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D138" s="27"/>
-      <c r="E138" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F138" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="G138" s="16"/>
+      <c r="B138" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="C138" s="69"/>
+      <c r="D138" s="70"/>
+      <c r="E138" s="71"/>
+      <c r="F138" s="72"/>
+      <c r="G138" s="88"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="14"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="40"/>
-      <c r="D139" s="46"/>
-      <c r="E139" s="45"/>
-      <c r="F139" s="49"/>
-      <c r="G139" s="16"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B139" s="76"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="64"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="66"/>
+      <c r="G139" s="87"/>
+    </row>
+    <row r="140" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="14"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="17"/>
-      <c r="F140" s="16"/>
-      <c r="G140" s="16"/>
+      <c r="B140" s="76"/>
+      <c r="C140" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="D140" s="40"/>
+      <c r="E140" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F140" s="66" t="s">
+        <v>118</v>
+      </c>
+      <c r="G140" s="87"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="14"/>
-      <c r="B141" s="18"/>
-      <c r="C141" s="38"/>
-      <c r="D141" s="60"/>
-      <c r="E141" s="43"/>
-      <c r="F141" s="47"/>
-      <c r="G141" s="16"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B141" s="76"/>
+      <c r="C141" s="67"/>
+      <c r="D141" s="64"/>
+      <c r="E141" s="65"/>
+      <c r="F141" s="66"/>
+      <c r="G141" s="87"/>
+    </row>
+    <row r="142" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="14"/>
-      <c r="B142" s="18"/>
-      <c r="C142" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D142" s="19"/>
-      <c r="E142" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F142" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="G142" s="16"/>
+      <c r="B142" s="76"/>
+      <c r="C142" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D142" s="53"/>
+      <c r="E142" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F142" s="66" t="s">
+        <v>119</v>
+      </c>
+      <c r="G142" s="87"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="14"/>
-      <c r="B143" s="18"/>
-      <c r="C143" s="39"/>
-      <c r="D143" s="37"/>
-      <c r="E143" s="44"/>
-      <c r="F143" s="48"/>
-      <c r="G143" s="16"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B143" s="76"/>
+      <c r="C143" s="67"/>
+      <c r="D143" s="64"/>
+      <c r="E143" s="65"/>
+      <c r="F143" s="66"/>
+      <c r="G143" s="87"/>
+    </row>
+    <row r="144" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="14"/>
-      <c r="B144" s="18"/>
-      <c r="C144" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D144" s="19"/>
-      <c r="E144" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F144" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="G144" s="16"/>
+      <c r="B144" s="76"/>
+      <c r="C144" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="D144" s="53"/>
+      <c r="E144" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F144" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="G144" s="87"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="14"/>
-      <c r="B145" s="18"/>
-      <c r="C145" s="40"/>
-      <c r="D145" s="46"/>
-      <c r="E145" s="45"/>
-      <c r="F145" s="49"/>
-      <c r="G145" s="16"/>
+      <c r="B145" s="76"/>
+      <c r="C145" s="67"/>
+      <c r="D145" s="64"/>
+      <c r="E145" s="65"/>
+      <c r="F145" s="66"/>
+      <c r="G145" s="87"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="14"/>
-      <c r="B146" s="18"/>
-      <c r="C146" s="53"/>
-      <c r="D146" s="54"/>
-      <c r="E146" s="55"/>
-      <c r="F146" s="54"/>
-      <c r="G146" s="16"/>
+      <c r="B146" s="76"/>
+      <c r="C146" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="D146" s="53"/>
+      <c r="E146" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F146" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="G146" s="87"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="14"/>
-      <c r="B147" s="18"/>
-      <c r="C147" s="38"/>
-      <c r="D147" s="60"/>
-      <c r="E147" s="43"/>
-      <c r="F147" s="47"/>
-      <c r="G147" s="16"/>
-    </row>
-    <row r="148" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B147" s="76"/>
+      <c r="C147" s="67"/>
+      <c r="D147" s="64"/>
+      <c r="E147" s="65"/>
+      <c r="F147" s="66"/>
+      <c r="G147" s="87"/>
+    </row>
+    <row r="148" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="14"/>
-      <c r="B148" s="18"/>
-      <c r="C148" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D148" s="28"/>
-      <c r="E148" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="F148" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="G148" s="16"/>
+      <c r="B148" s="76"/>
+      <c r="C148" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="D148" s="53"/>
+      <c r="E148" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F148" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G148" s="87"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="14"/>
-      <c r="B149" s="18"/>
-      <c r="C149" s="40"/>
-      <c r="D149" s="46"/>
-      <c r="E149" s="45"/>
-      <c r="F149" s="49"/>
-      <c r="G149" s="16"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B149" s="76"/>
+      <c r="C149" s="67"/>
+      <c r="D149" s="64"/>
+      <c r="E149" s="65"/>
+      <c r="F149" s="66"/>
+      <c r="G149" s="87"/>
+    </row>
+    <row r="150" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A150" s="14"/>
-      <c r="B150" s="18"/>
-      <c r="C150" s="15"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-    </row>
-    <row r="151" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="20"/>
-      <c r="C151" s="22"/>
-      <c r="D151" s="23"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="25"/>
-      <c r="G151" s="25"/>
-    </row>
-    <row r="152" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="14"/>
-      <c r="B152" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C152" s="34"/>
-      <c r="D152" s="16"/>
-      <c r="E152" s="17"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-    </row>
+      <c r="B150" s="76"/>
+      <c r="C150" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="D150" s="53"/>
+      <c r="E150" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F150" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="G150" s="87"/>
+    </row>
+    <row r="151" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="14"/>
+      <c r="B151" s="77"/>
+      <c r="C151" s="78"/>
+      <c r="D151" s="79"/>
+      <c r="E151" s="80"/>
+      <c r="F151" s="81"/>
+      <c r="G151" s="82"/>
+    </row>
+    <row r="152" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="153" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="14"/>
-      <c r="B153" s="18"/>
-      <c r="C153" s="15"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="17"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-    </row>
-    <row r="154" spans="1:7" s="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="10"/>
-      <c r="B154" s="52"/>
-      <c r="C154" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="D154" s="29"/>
-      <c r="E154" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="F154" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="G154" s="54"/>
-    </row>
-    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="C153" s="63"/>
+      <c r="D153" s="64"/>
+      <c r="E153" s="65"/>
+      <c r="F153" s="66"/>
+      <c r="G153" s="66"/>
+    </row>
+    <row r="154" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="14"/>
+      <c r="B154" s="83"/>
+      <c r="C154" s="67"/>
+      <c r="D154" s="64"/>
+      <c r="E154" s="65"/>
+      <c r="F154" s="66"/>
+      <c r="G154" s="66"/>
+    </row>
+    <row r="155" spans="1:7" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="14"/>
-      <c r="B155" s="18"/>
-      <c r="C155" s="15"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="17"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-    </row>
-    <row r="156" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="83"/>
+      <c r="C155" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="40"/>
+      <c r="E155" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F155" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="G155" s="66"/>
+    </row>
+    <row r="156" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="14"/>
-      <c r="B156" s="18"/>
-      <c r="C156" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D156" s="19"/>
-      <c r="E156" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F156" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="G156" s="16"/>
-    </row>
-    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="83"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="64"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="66"/>
+      <c r="G156" s="66"/>
+    </row>
+    <row r="157" spans="1:7" s="16" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="14"/>
-      <c r="B157" s="18"/>
-      <c r="C157" s="15"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="17"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="16"/>
-    </row>
-    <row r="158" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="83"/>
+      <c r="C157" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D157" s="40"/>
+      <c r="E157" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="F157" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="G157" s="66"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="14"/>
-      <c r="B158" s="18"/>
-      <c r="C158" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D158" s="19"/>
-      <c r="E158" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G158" s="16"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B158" s="83"/>
+      <c r="C158" s="67"/>
+      <c r="D158" s="64"/>
+      <c r="E158" s="65"/>
+      <c r="F158" s="66"/>
+      <c r="G158" s="66"/>
+    </row>
+    <row r="159" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="14"/>
-      <c r="B159" s="18"/>
-      <c r="C159" s="15"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="16"/>
-    </row>
-    <row r="160" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B159" s="83"/>
+      <c r="C159" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D159" s="40"/>
+      <c r="E159" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="G159" s="66"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="14"/>
-      <c r="B160" s="18"/>
-      <c r="C160" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D160" s="19"/>
-      <c r="E160" s="17" t="s">
+      <c r="B160" s="83"/>
+      <c r="C160" s="67"/>
+      <c r="D160" s="64"/>
+      <c r="E160" s="65"/>
+      <c r="F160" s="66"/>
+      <c r="G160" s="66"/>
+    </row>
+    <row r="161" spans="1:7" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="B161" s="83"/>
+      <c r="C161" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D161" s="53"/>
+      <c r="E161" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F161" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="F160" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="G160" s="16"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="14"/>
-      <c r="B161" s="18"/>
-      <c r="C161" s="15"/>
-      <c r="D161" s="16"/>
-      <c r="E161" s="17"/>
-      <c r="F161" s="16"/>
-      <c r="G161" s="16"/>
-    </row>
-    <row r="162" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B162" s="18"/>
-      <c r="C162" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D162" s="28"/>
-      <c r="E162" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F162" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G162" s="16"/>
-    </row>
-    <row r="163" spans="1:7" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="10"/>
-      <c r="B163" s="52"/>
-      <c r="C163" s="53"/>
-      <c r="D163" s="54"/>
-      <c r="E163" s="55"/>
-      <c r="F163" s="54"/>
-      <c r="G163" s="54"/>
-    </row>
-    <row r="164" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G161" s="66"/>
+    </row>
+    <row r="162" spans="1:7" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="10"/>
+      <c r="B162" s="94"/>
+      <c r="C162" s="89"/>
+      <c r="D162" s="91"/>
+      <c r="E162" s="92"/>
+      <c r="F162" s="84"/>
+      <c r="G162" s="84"/>
+    </row>
+    <row r="163" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A163" s="14"/>
+      <c r="B163" s="83"/>
+      <c r="C163" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D163" s="40"/>
+      <c r="E163" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F163" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="G163" s="66"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="14"/>
-      <c r="B164" s="18"/>
-      <c r="C164" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D164" s="19"/>
-      <c r="E164" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F164" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G164" s="16"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B164" s="83"/>
+      <c r="C164" s="67"/>
+      <c r="D164" s="64"/>
+      <c r="E164" s="65"/>
+      <c r="F164" s="66"/>
+      <c r="G164" s="66"/>
+    </row>
+    <row r="165" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A165" s="14"/>
-      <c r="B165" s="18"/>
-      <c r="C165" s="15"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="17"/>
-      <c r="F165" s="16"/>
-      <c r="G165" s="16"/>
-    </row>
-    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B165" s="83"/>
+      <c r="C165" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="D165" s="40"/>
+      <c r="E165" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="F165" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="G165" s="66"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
-      <c r="B166" s="18"/>
-      <c r="C166" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D166" s="19"/>
-      <c r="E166" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="F166" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G166" s="16"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="14"/>
-      <c r="B167" s="18"/>
-      <c r="C167" s="15"/>
-      <c r="D167" s="54"/>
-      <c r="E167" s="17"/>
-      <c r="F167" s="16"/>
-      <c r="G167" s="16"/>
+      <c r="B166" s="83"/>
+      <c r="C166" s="67"/>
+      <c r="D166" s="91"/>
+      <c r="E166" s="65"/>
+      <c r="F166" s="66"/>
+      <c r="G166" s="66"/>
+    </row>
+    <row r="167" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="168" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="14"/>
+      <c r="B168" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C168" s="69"/>
+      <c r="D168" s="70"/>
+      <c r="E168" s="71"/>
+      <c r="F168" s="72"/>
+      <c r="G168" s="88"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="14"/>
-      <c r="B169" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="C169" s="34"/>
-      <c r="D169" s="16"/>
-      <c r="E169" s="17"/>
-      <c r="F169" s="16"/>
-      <c r="G169" s="16"/>
+      <c r="B169" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C169" s="63"/>
+      <c r="D169" s="64"/>
+      <c r="E169" s="65"/>
+      <c r="F169" s="66"/>
+      <c r="G169" s="87"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="14"/>
-      <c r="B170" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C170" s="34"/>
-      <c r="D170" s="16"/>
-      <c r="E170" s="17"/>
-      <c r="F170" s="16"/>
-      <c r="G170" s="16"/>
+      <c r="B170" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="C170" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="D170" s="64"/>
+      <c r="E170" s="65"/>
+      <c r="F170" s="66"/>
+      <c r="G170" s="87"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="14"/>
-      <c r="B171" s="18"/>
-      <c r="C171" s="15"/>
-      <c r="D171" s="16"/>
-      <c r="E171" s="17"/>
-      <c r="F171" s="16"/>
-      <c r="G171" s="16"/>
+      <c r="B171" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="C171" s="95" t="s">
+        <v>129</v>
+      </c>
+      <c r="D171" s="64"/>
+      <c r="E171" s="65"/>
+      <c r="F171" s="66"/>
+      <c r="G171" s="87"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="14"/>
-      <c r="B172" s="18"/>
-      <c r="C172" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D172" s="19"/>
-      <c r="E172" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F172" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G172" s="16"/>
+      <c r="B172" s="76"/>
+      <c r="C172" s="67"/>
+      <c r="D172" s="64"/>
+      <c r="E172" s="65"/>
+      <c r="F172" s="66"/>
+      <c r="G172" s="87"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="14"/>
-      <c r="B173" s="18"/>
-      <c r="C173" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D173" s="19"/>
-      <c r="E173" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F173" s="16"/>
-      <c r="G173" s="16"/>
+      <c r="B173" s="76"/>
+      <c r="C173" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D173" s="40"/>
+      <c r="E173" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F173" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="G173" s="87"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="14"/>
-      <c r="B174" s="18"/>
-      <c r="C174" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D174" s="19"/>
-      <c r="E174" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F174" s="16"/>
-      <c r="G174" s="16"/>
+      <c r="B174" s="76"/>
+      <c r="C174" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D174" s="40"/>
+      <c r="E174" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F174" s="66"/>
+      <c r="G174" s="87"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="14"/>
-      <c r="B175" s="18"/>
-      <c r="C175" s="15"/>
-      <c r="D175" s="16"/>
-      <c r="E175" s="17"/>
-      <c r="F175" s="16"/>
-      <c r="G175" s="16"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B175" s="76"/>
+      <c r="C175" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D175" s="40"/>
+      <c r="E175" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F175" s="66"/>
+      <c r="G175" s="87"/>
+    </row>
+    <row r="176" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="14"/>
-      <c r="B176" s="18"/>
-      <c r="C176" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D176" s="19"/>
-      <c r="E176" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F176" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="G176" s="16"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="14"/>
-      <c r="B177" s="18"/>
-      <c r="C177" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D177" s="19"/>
-      <c r="E177" s="17"/>
-      <c r="F177" s="16"/>
-      <c r="G177" s="16"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="14"/>
-      <c r="B178" s="18"/>
-      <c r="C178" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D178" s="19"/>
-      <c r="E178" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F178" s="16"/>
-      <c r="G178" s="16"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="14"/>
-      <c r="B179" s="18"/>
-      <c r="C179" s="15"/>
-      <c r="D179" s="16"/>
-      <c r="E179" s="17"/>
-      <c r="F179" s="16"/>
-      <c r="G179" s="16"/>
-    </row>
-    <row r="180" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="9"/>
-      <c r="C180" s="30"/>
-      <c r="D180" s="31"/>
-      <c r="E180" s="32"/>
-      <c r="F180" s="31"/>
-      <c r="G180" s="31"/>
-    </row>
-    <row r="181" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C181" s="5"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
+      <c r="B176" s="77"/>
+      <c r="C176" s="78"/>
+      <c r="D176" s="79"/>
+      <c r="E176" s="80"/>
+      <c r="F176" s="81"/>
+      <c r="G176" s="82"/>
+    </row>
+    <row r="177" spans="1:7" s="14" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="9"/>
+      <c r="C177" s="17"/>
+      <c r="D177" s="55"/>
+      <c r="E177" s="19"/>
+      <c r="F177" s="18"/>
+      <c r="G177" s="18"/>
+    </row>
+    <row r="178" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C178" s="5"/>
+      <c r="D178" s="38"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="6"/>
+      <c r="G178" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
